--- a/redmine-logger/backend/input.xlsx
+++ b/redmine-logger/backend/input.xlsx
@@ -8,19 +8,19 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Tasks" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t xml:space="preserve">comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_id</t>
   </si>
   <si>
     <t xml:space="preserve">YTP - LA height and weight entered details  are not appearing after recalculating BI from Review Details screen and the Make Payment screen.</t>
@@ -103,13 +106,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,74 +132,21 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF2D0"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FF993300"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -226,28 +175,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -255,19 +184,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -280,66 +197,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFDAF2D0"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -354,44 +211,44 @@
         <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -405,63 +262,51 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -479,34 +324,46 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
+                <a:shade val="20000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -520,13 +377,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E57"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="47.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -542,162 +396,364 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="1" t="n">
         <v>46177</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>14</v>
+      <c r="D12" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="7" t="s">
-        <v>15</v>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="7" t="s">
-        <v>16</v>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="7" t="s">
-        <v>17</v>
+      <c r="D15" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="8" t="s">
-        <v>18</v>
+      <c r="D16" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="9" t="s">
-        <v>19</v>
+      <c r="D17" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D20" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="7" t="s">
-        <v>22</v>
+      <c r="D21" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="7" t="s">
-        <v>23</v>
+      <c r="D22" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D23" s="7" t="s">
-        <v>24</v>
+      <c r="D23" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>

--- a/redmine-logger/backend/input.xlsx
+++ b/redmine-logger/backend/input.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E81"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -1094,9 +1094,434 @@
         <v>9f4b41ecdd9cd9d1c7b5100c0502cb80b744e607</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B57" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1</v>
+      </c>
+      <c r="D57" s="1" t="str">
+        <v>deployment setup</v>
+      </c>
+      <c r="E57" s="1" t="str">
+        <v>1f619869b38ffd400abae6d7d1eb61163946728a</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B58" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="1" t="str">
+        <v>MVP-1</v>
+      </c>
+      <c r="E58" s="1" t="str">
+        <v>9e26a2e2d3d2633de8816a12e501299931a3485b</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B59" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <v>working fine</v>
+      </c>
+      <c r="E59" s="1" t="str">
+        <v>c06603001ddd34dda0667adcf9e968290a45863e</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B60" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1" t="str">
+        <v>ui fix</v>
+      </c>
+      <c r="E60" s="1" t="str">
+        <v>02e12417a80bff020e0cdae272c5185255fcd3bc</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B61" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C61" s="1">
+        <v>1</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <v>apu sheet creation</v>
+      </c>
+      <c r="E61" s="1" t="str">
+        <v>856676533897f232eb2c0153b6d570adef0a7310</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B62" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <v>commit fetch done</v>
+      </c>
+      <c r="E62" s="1" t="str">
+        <v>d6a26a233e1d1c46a4bbc6e2b34c4fb168a14a9c</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="B63" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1" t="str">
+        <v>commit fetch api inprocess</v>
+      </c>
+      <c r="E63" s="1" t="str">
+        <v>daf6463f1004e2725a82357bd4957c35630d104d</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B64" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1" t="str">
+        <v>Merge branch 'insure/develop' into uat-common-backend-1</v>
+      </c>
+      <c r="E64" s="1" t="str">
+        <v>569367c297664fb8166da5ce886645b0f91f7a07</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B65" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1" t="str">
+        <v>Merge branch 'ISNP2.0-viewDoc' into insure/develop</v>
+      </c>
+      <c r="E65" s="1" t="str">
+        <v>97ec690b39cc3d63bf6f87d850cd6d0c165ef92e</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="B66" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="1" t="str">
+        <v>view doc</v>
+      </c>
+      <c r="E66" s="1" t="str">
+        <v>d8ba6ebbed9e1c2488d60aa58f94bd2b07b09bca</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B67" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <v>create excel and logtime both</v>
+      </c>
+      <c r="E67" s="1" t="str">
+        <v>61dfdfc39dc43953751d111a5a2845738dca7310</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B68" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <v>redmine logtime in a issue</v>
+      </c>
+      <c r="E68" s="1" t="str">
+        <v>e72a844d056a18654bda7f35813b1b82dadbe11d</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="B69" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="1" t="str">
+        <v>first commit</v>
+      </c>
+      <c r="E69" s="1" t="str">
+        <v>6ed7832a91ea9c94b8bcd0be5a0ba8ae1a56b347</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B70" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1</v>
+      </c>
+      <c r="D70" s="1" t="str">
+        <v>change in fm and rm</v>
+      </c>
+      <c r="E70" s="1" t="str">
+        <v>d9abbb744e8db8ed76923c3097a01bad0d6611fb</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B71" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="1" t="str">
+        <v>Merge branch 'insure-api-wrapper' of https://github.com/lumiqai/isnp-backend-v2 into insure-api-wrapper</v>
+      </c>
+      <c r="E71" s="1" t="str">
+        <v>f135d9f9bf66647b7227ceeddd7c064bfe0dd9f4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B72" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1</v>
+      </c>
+      <c r="D72" s="1" t="str">
+        <v>retailduplicateApplicationNumber</v>
+      </c>
+      <c r="E72" s="1" t="str">
+        <v>6b42e2097e52b2fc8bca0b8369923e986ee4fa4f</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B73" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1</v>
+      </c>
+      <c r="D73" s="1" t="str">
+        <v>application number exist api</v>
+      </c>
+      <c r="E73" s="1" t="str">
+        <v>61672101b8bc72d019e4194c25c8471a8eb7db00</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B74" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" s="1" t="str">
+        <v>rename route for insure2</v>
+      </c>
+      <c r="E74" s="1" t="str">
+        <v>69c09dbd6ddc08e72e384b683c0dd09f64f36272</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B75" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="1" t="str">
+        <v>make pan wrapper generic</v>
+      </c>
+      <c r="E75" s="1" t="str">
+        <v>109771a04b7823cb8b195828bfe51e7acc4e77d5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B76" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C76" s="1">
+        <v>1</v>
+      </c>
+      <c r="D76" s="1" t="str">
+        <v>generic wrapper</v>
+      </c>
+      <c r="E76" s="1" t="str">
+        <v>0db337c779bb5b41c01d6792d5a89d2164677964</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B77" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C77" s="1">
+        <v>1</v>
+      </c>
+      <c r="D77" s="1" t="str">
+        <v>new routes for ISNP2.0</v>
+      </c>
+      <c r="E77" s="1" t="str">
+        <v>46369462a4a27be7e4a52103b3ea980ad7d1bde8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="B78" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C78" s="1">
+        <v>1</v>
+      </c>
+      <c r="D78" s="1" t="str">
+        <v>Merge branch 'CR-36689-backend' into uat-common-backend-1</v>
+      </c>
+      <c r="E78" s="1" t="str">
+        <v>c13893e09868c8e55a880da96b2d1c8ed842bd12</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="B79" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C79" s="1">
+        <v>1</v>
+      </c>
+      <c r="D79" s="1" t="str">
+        <v>proposal form photo</v>
+      </c>
+      <c r="E79" s="1" t="str">
+        <v>728198965083920c53df98ecd079c966f9582b55</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B80" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C80" s="1">
+        <v>1</v>
+      </c>
+      <c r="D80" s="1" t="str">
+        <v>Merge remote-tracking branch 'origin/CR-36689-backend' into uat-common-backend-1</v>
+      </c>
+      <c r="E80" s="1" t="str">
+        <v>b45e6c1d56d0c7977c25dde43e5533c3473350cd</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B81" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C81" s="1">
+        <v>1</v>
+      </c>
+      <c r="D81" s="1" t="str">
+        <v>LA=&gt;PR in proposal form</v>
+      </c>
+      <c r="E81" s="1" t="str">
+        <v>9eacdfea71d2af341bf4d5f68ef3baa57f34a750</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E81"/>
   </ignoredErrors>
 </worksheet>
 </file>